--- a/planilhas/Auditoria de Landing Page - V4.xlsx
+++ b/planilhas/Auditoria de Landing Page - V4.xlsx
@@ -735,7 +735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1444,160 +1444,296 @@
       </c>
       <c r="H25" s="9" t="inlineStr"/>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr"/>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Nível de consciência compatível com a origem do tráfego</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>Descubra de onde vem o tráfego (frio de interesses, remarketing, busca por marca) e leia a página como essa pessoa. Tráfego frio precisa do problema antes da solução; tráfego de fundo já quer preço e prazo. Falar de produto com quem ainda não sabe que tem o problema é a quebra mais cara e mais comum.</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>Copy no nível de consciência de quem chega</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>Reescreva a primeira dobra no nível certo, ou separe a página por origem de tráfego. Uma LP não atende frio e fundo ao mesmo tempo.</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>Crítico</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Mecanismo explicado (por que funciona), não só o resultado</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Procure a explicação do COMO. Promessa sem mecanismo soa como qualquer concorrente e não vence ceticismo — sobretudo em ticket alto ou nicho saturado.</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Mecanismo nomeado e explicado em 1 bloco</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Nomeie o método/processo e explique em 3 a 5 linhas por que ele produz o resultado prometido.</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr"/>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Teste da substituição: a copy é do cliente ou serve para qualquer um?</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>Troque mentalmente o nome da empresa pelo de um concorrente. Se o texto continua funcionando, ele não diz nada de específico. Procure número, prazo, nome, situação concreta.</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>Copy que só funciona para este negócio</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>Substitua adjetivo por especificidade: resultado com número, prazo real, situação concreta do cliente.</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>Importante</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr"/>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Linguagem genérica ou com cara de texto gerado por IA</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Procure palavras de enchimento (incrível, revolucionário, transformador), clichês sem prova (resultados comprovados, método definitivo, oportunidade única), frases binárias ('não é só X. É Y.') e pergunta retórica na abertura. Texto que soa artificial derruba confiança justamente em quem está decidindo.</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Sem clichê de mercado e sem padrão de texto gerado</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>Reescreva no concreto: o que acontece, para quem, em quanto tempo. Corte adjetivo sem prova.</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Bom ter</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>1.5 Confiança e conformidade</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr"/>
-      <c r="B27" s="7" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr"/>
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>Política de privacidade e LGPD</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>Confira link visível para a política de privacidade e a base legal de coleta de dados. Obrigatório ao captar leads no Brasil.</t>
         </is>
       </c>
-      <c r="D27" s="7" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Política acessível + base LGPD</t>
         </is>
       </c>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>Publique a política de privacidade e linke no formulário e no rodapé.</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t>Importante</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr"/>
-      <c r="B28" s="9" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr"/>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Consentimento na coleta de dados</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
         <is>
           <t>Veja se há consentimento explícito (checkbox/aviso) para o uso dos dados e contato. Consentimento protege a operação.</t>
         </is>
       </c>
-      <c r="D28" s="9" t="inlineStr">
+      <c r="D32" s="9" t="inlineStr">
         <is>
           <t>Consentimento explícito no formulário</t>
         </is>
       </c>
-      <c r="E28" s="9" t="inlineStr">
+      <c r="E32" s="9" t="inlineStr">
         <is>
           <t>Adicione aviso/checkbox de consentimento com link para a política.</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F32" s="8" t="inlineStr">
         <is>
           <t>Importante</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="inlineStr"/>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr"/>
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Sinais de confiança: selos, garantia e contato visível</t>
         </is>
       </c>
-      <c r="C29" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>Confira selos de segurança, garantia e certificações que reduzam o risco percebido, e se há um canal de contato (WhatsApp, e-mail, telefone). Ausência total de contato gera desconfiança.</t>
         </is>
       </c>
-      <c r="D29" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Selos/garantia + ao menos 1 canal de contato</t>
         </is>
       </c>
-      <c r="E29" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>Inclua selos reais e garantia clara perto do CTA; adicione um canal de contato que funcione.</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>Bom ter</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr"/>
-      <c r="B30" s="9" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr"/>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Coerência visual com a marca</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
         <is>
           <t>Compare cores, tipografia e logo da LP com a identidade da marca e do anúncio. Inconsistência sinaliza amadorismo.</t>
         </is>
       </c>
-      <c r="D30" s="9" t="inlineStr">
+      <c r="D34" s="9" t="inlineStr">
         <is>
           <t>Identidade alinhada à marca e ao anúncio</t>
         </is>
       </c>
-      <c r="E30" s="9" t="inlineStr">
+      <c r="E34" s="9" t="inlineStr">
         <is>
           <t>Padronize logo, paleta e tipografia conforme o manual da marca.</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F34" s="8" t="inlineStr">
         <is>
           <t>Bom ter</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>Pendente</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr"/>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Pendente</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A10:H10"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G30">
+  <conditionalFormatting sqref="G4:G34">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -1614,7 +1750,7 @@
       <formula>"Pendente"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F30">
+  <conditionalFormatting sqref="F4:F34">
     <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
       <formula>"Crítico"</formula>
     </cfRule>
@@ -1625,16 +1761,16 @@
       <formula>"Bom ter"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A4:A30">
+  <conditionalFormatting sqref="A4:A34">
     <cfRule type="expression" priority="9" dxfId="0">
       <formula>A4="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="G4:G30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="G4:G34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$A$1:$A$5</formula1>
     </dataValidation>
-    <dataValidation sqref="A4:A30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="A4:A34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>_Listas!$B$1:$B$1</formula1>
     </dataValidation>
   </dataValidations>
